--- a/consent_forms/034_event_waiver_form--consent_forms.xlsx
+++ b/consent_forms/034_event_waiver_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Event Waiver Form Part 1</t>
+          <t>Brief Description of the Event</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Participant</t>
+          <t>Select the Participant</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Event Waiver Form Part 2</t>
+          <t>Understanding and Agreement</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Participant</t>
+          <t>Select All Participants</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk Description</t>
+          <t>Describe the Potential Risks</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk Description</t>
+          <t>Describe Additional Risks</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Reviewed and Agreed</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +686,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Signed and Agreed</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Acknowledged and Agreed</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -792,17 +792,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>participant_part_2_choices</t>
+          <t>participant_part_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>participant_1</t>
+          <t>participant_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Participant 1</t>
+          <t>Participant 3</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>participant_2</t>
+          <t>participant_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Participant 2</t>
+          <t>Participant 1</t>
         </is>
       </c>
     </row>
@@ -831,29 +831,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>participant_3</t>
+          <t>participant_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Participant 3</t>
+          <t>Participant 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>signature_part_1_choices</t>
+          <t>participant_part_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>participant_1</t>
+          <t>participant_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Participant 1</t>
+          <t>Participant 3</t>
         </is>
       </c>
     </row>
@@ -865,29 +865,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>participant_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Participant 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>signature_part_2_choices</t>
+          <t>signature_part_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -899,29 +899,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>signature_part_3_choices</t>
+          <t>signature_part_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -933,10 +933,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>signature_part_3_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
